--- a/DeepXen/Xenopus/TSS_Deeper_updated/RunningExps.xlsx
+++ b/DeepXen/Xenopus/TSS_Deeper_updated/RunningExps.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christopherpenfold/Desktop/Code/DeepXen/DeepXen/Xenopus/TSS_Deeper_updated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD86AAA-951E-DA4C-91EF-AFF7051422D9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C05DF19-F914-DA4D-BA6D-EB1F7831909B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="1460" windowWidth="21280" windowHeight="17620" xr2:uid="{E8C7C579-6A0A-814E-9ADD-5E5CC4C9C093}"/>
   </bookViews>
@@ -33,10 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="9">
-  <si>
-    <t>Output</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="10">
   <si>
     <t>Status</t>
   </si>
@@ -47,9 +44,6 @@
     <t>Input chr</t>
   </si>
   <si>
-    <t>Input exp</t>
-  </si>
-  <si>
     <t>Endo</t>
   </si>
   <si>
@@ -60,6 +54,15 @@
   </si>
   <si>
     <t>D</t>
+  </si>
+  <si>
+    <t>Input expression</t>
+  </si>
+  <si>
+    <t>Output list</t>
+  </si>
+  <si>
+    <t>R</t>
   </si>
 </sst>
 </file>
@@ -413,101 +416,104 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9FDB6FC-9FC7-3B41-B5C1-9CDF7C234669}">
   <dimension ref="B1:F23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="14.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>0</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -515,13 +521,13 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -529,41 +535,41 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10">
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -571,13 +577,13 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -585,41 +591,41 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E14">
         <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -627,13 +633,13 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -641,41 +647,41 @@
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -683,13 +689,13 @@
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -697,30 +703,30 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
